--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486439_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486439_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6829</v>
+        <v>2.6678</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6231</v>
+        <v>3.3458</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9402</v>
+        <v>-0.678</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9276</v>
+        <v>1.8371</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1124</v>
+        <v>1.7789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8152</v>
+        <v>0.0582</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5239</v>
+        <v>5.2192</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7117</v>
+        <v>2.4637</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8121</v>
+        <v>2.7556</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5963</v>
+        <v>-3.3821</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5994</v>
+        <v>-0.6847</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.9969</v>
+        <v>-2.6974</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0924</v>
+        <v>-1.3444</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.7859</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.5585</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5392</v>
+        <v>1.739</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5563</v>
+        <v>2.6484</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0171</v>
+        <v>-0.9094</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8371</v>
+        <v>0.9276</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7789</v>
+        <v>0.1124</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0582</v>
+        <v>0.8152</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2192</v>
+        <v>3.5239</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4637</v>
+        <v>0.7117</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7556</v>
+        <v>2.8121</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3821</v>
+        <v>-2.5963</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6847</v>
+        <v>-0.5994</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.6974</v>
+        <v>-1.9969</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2626</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.473</v>
+        <v>-0.0363</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5754</v>
+        <v>0.0168</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8976</v>
+        <v>-0.0532</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3283</v>
+        <v>0.0521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1226</v>
+        <v>0.2164</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2056</v>
+        <v>-0.1643</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0112</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0531</v>
+        <v>-0.3293</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2019</v>
+        <v>-0.1081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1488</v>
+        <v>-0.2211</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2814</v>
+        <v>-1.6838</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7445000000000001</v>
+        <v>-0.8134</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0259</v>
+        <v>-0.8704</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6299</v>
+        <v>-2.2618</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2523</v>
+        <v>-1.1526</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8822</v>
+        <v>-1.1092</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8844</v>
+        <v>-0.8314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7696</v>
+        <v>-0.8696</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1147</v>
+        <v>0.0382</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5143</v>
+        <v>-1.4304</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5173</v>
+        <v>-0.2829</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9969</v>
+        <v>-1.1475</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4779</v>
+        <v>0.143</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5997</v>
+        <v>0.018</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1217</v>
+        <v>0.125</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8695</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7292</v>
+        <v>-1.775</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1054</v>
+        <v>-0.7284</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6238</v>
+        <v>-1.0466</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2618</v>
+        <v>-0.8022</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1526</v>
+        <v>-0.0213</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1092</v>
+        <v>-0.7809</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8314</v>
+        <v>0.4331</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8696</v>
+        <v>0.2801</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>0.153</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4304</v>
+        <v>-1.2353</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2829</v>
+        <v>-0.3013</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1475</v>
+        <v>-0.9339</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>-0.2692</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3716</v>
+        <v>-0.2485</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9115</v>
+        <v>-1.7957</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0239</v>
+        <v>0.3227</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-2.1184</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4048</v>
+        <v>-1.6299</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2191</v>
+        <v>0.2523</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6239</v>
+        <v>-1.8822</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4145</v>
+        <v>0.8844</v>
       </c>
       <c r="K7" t="n">
-        <v>0.338</v>
+        <v>0.7696</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8193</v>
+        <v>-2.5143</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1188</v>
+        <v>-0.5173</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7004</v>
+        <v>-1.9969</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4933</v>
+        <v>-0.0363</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7367</v>
+        <v>0.1779</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2434</v>
+        <v>-0.2142</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>-1.8695</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X7" t="n">
         <v>-1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4082</v>
+        <v>-2.6677</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2692</v>
+        <v>-1.626</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1391</v>
+        <v>-1.0417</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8022</v>
+        <v>-0.4048</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0213</v>
+        <v>0.2191</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7809</v>
+        <v>-0.6239</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4331</v>
+        <v>0.4145</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2801</v>
+        <v>0.338</v>
       </c>
       <c r="L8" t="n">
-        <v>0.153</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2353</v>
+        <v>-0.8193</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3013</v>
+        <v>-0.1188</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9339</v>
+        <v>-0.7004</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1509</v>
+        <v>-0.2629</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8099</v>
+        <v>0.1346</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3409</v>
+        <v>-0.3975</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5204</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2713</v>
+        <v>-3.0052</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9098</v>
+        <v>-1.767</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3615</v>
+        <v>-1.2382</v>
       </c>
       <c r="G9" t="n">
         <v>-4.4504</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6458</v>
+        <v>-0.3797</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8784</v>
+        <v>0.2644</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7674</v>
+        <v>-0.6441</v>
       </c>
       <c r="V9" t="n">
         <v>2.2599</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,37 +1189,37 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6069</v>
+        <v>-4.9554</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8629</v>
+        <v>-3.8576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.256</v>
+        <v>-1.0978</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.1278</v>
+        <v>-5.062</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2805</v>
+        <v>-5.0637</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.8473</v>
+        <v>0.0016</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.0566</v>
+        <v>-3.4434</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9942</v>
+        <v>-4.2299</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.0624</v>
+        <v>0.7865</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0712</v>
+        <v>-1.6187</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2863</v>
+        <v>-0.8337</v>
       </c>
       <c r="O10" t="n">
         <v>-0.7849</v>
@@ -1234,28 +1234,28 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3033</v>
+        <v>-0.9809</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1512</v>
+        <v>-0.4566</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8479</v>
+        <v>-0.5242</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,37 +1267,37 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8738</v>
+        <v>-5.3957</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6219</v>
+        <v>-5.775</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2519</v>
+        <v>0.3793</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.062</v>
+        <v>-7.1278</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.0637</v>
+        <v>-1.2805</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0016</v>
+        <v>-5.8473</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4434</v>
+        <v>-6.0566</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.2299</v>
+        <v>-0.9942</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7865</v>
+        <v>-5.0624</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6187</v>
+        <v>-1.0712</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8337</v>
+        <v>-0.2863</v>
       </c>
       <c r="O11" t="n">
         <v>-0.7849</v>
@@ -1312,22 +1312,22 @@
         <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8993</v>
+        <v>-0.4855</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2209</v>
+        <v>0.2392</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6784</v>
+        <v>-0.7246</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.5319</v>
+        <v>-16.8196</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.746600000000001</v>
+        <v>-8.0341</v>
       </c>
       <c r="F12" t="n">
         <v>-8.785499999999999</v>
@@ -1363,13 +1363,13 @@
         <v>-12.4428</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.648</v>
+        <v>-1.648000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-3.1144</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4662</v>
+        <v>1.466200000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-18.3375</v>
@@ -1390,13 +1390,13 @@
         <v>18.4883</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.9424</v>
+        <v>-4.2299</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4813</v>
+        <v>-0.7688999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4609</v>
+        <v>-3.460900000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3046</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.665</v>
+        <v>5.6535</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4675</v>
+        <v>4.5792</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1975</v>
+        <v>1.0742</v>
       </c>
       <c r="G13" t="n">
         <v>4.7077</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3047</v>
+        <v>0.2932</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6352</v>
+        <v>0.5119</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4935</v>
+        <v>4.3922</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5085</v>
+        <v>4.7716</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9851</v>
+        <v>-0.3795</v>
       </c>
       <c r="G14" t="n">
-        <v>2.633</v>
+        <v>3.793</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7604</v>
+        <v>1.5602</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8726</v>
+        <v>2.2328</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8657</v>
+        <v>3.7668</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1008</v>
+        <v>1.2806</v>
       </c>
       <c r="L14" t="n">
-        <v>0.765</v>
+        <v>2.4862</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7673</v>
+        <v>0.0262</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6597</v>
+        <v>0.2796</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1076</v>
+        <v>-0.2534</v>
       </c>
       <c r="P14" t="n">
         <v>0.87</v>
@@ -1546,28 +1546,28 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1204</v>
+        <v>0.2941</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5128</v>
+        <v>0.4398</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6077</v>
+        <v>-0.1457</v>
       </c>
       <c r="V14" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="X14" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-2.2599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5533</v>
+        <v>3.789</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9893</v>
+        <v>3.0556</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.436</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>3.793</v>
+        <v>2.633</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5602</v>
+        <v>0.7604</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2328</v>
+        <v>1.8726</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7668</v>
+        <v>0.8657</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2806</v>
+        <v>0.1008</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4862</v>
+        <v>0.765</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0262</v>
+        <v>1.7673</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2796</v>
+        <v>0.6597</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2534</v>
+        <v>1.1076</v>
       </c>
       <c r="P15" t="n">
         <v>0.87</v>
@@ -1624,22 +1624,22 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5447</v>
+        <v>1.4159</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3425</v>
+        <v>1.0599</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2023</v>
+        <v>0.356</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1538</v>
+        <v>3.0844</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2419</v>
+        <v>2.0183</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9119</v>
+        <v>1.066</v>
       </c>
       <c r="G16" t="n">
         <v>0.3321</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2143</v>
+        <v>1.1449</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1476</v>
+        <v>0.9241</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0667</v>
+        <v>0.2208</v>
       </c>
       <c r="V16" t="n">
         <v>2.2599</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1401</v>
+        <v>2.6931</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1439</v>
+        <v>0.6969</v>
       </c>
       <c r="F17" t="n">
         <v>1.9962</v>
@@ -1780,10 +1780,10 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.858</v>
+        <v>0.411</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4146</v>
+        <v>-0.0324</v>
       </c>
       <c r="U17" t="n">
         <v>0.4434</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2011</v>
+        <v>2.4527</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3145</v>
+        <v>1.8928</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5156</v>
+        <v>0.5598</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8277</v>
+        <v>2.0246</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6903</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.518</v>
+        <v>2.8185</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3746</v>
+        <v>3.0128</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4655</v>
+        <v>-0.5261</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0909</v>
+        <v>3.5389</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2023</v>
+        <v>-0.9882</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7752</v>
+        <v>-0.2679</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4271</v>
+        <v>-0.7204</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9384</v>
+        <v>0.4281</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2776</v>
+        <v>-0.0324</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.4605</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0365</v>
+        <v>1.9299</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4458</v>
+        <v>0.3353</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5907</v>
+        <v>1.5945</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0246</v>
+        <v>4.4067</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7939000000000001</v>
+        <v>2.7979</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8185</v>
+        <v>1.6088</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0128</v>
+        <v>3.7694</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5261</v>
+        <v>2.3542</v>
       </c>
       <c r="L19" t="n">
-        <v>3.5389</v>
+        <v>1.4152</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9882</v>
+        <v>0.6373</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2679</v>
+        <v>0.4437</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7204</v>
+        <v>0.1936</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-5.4377</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0119</v>
+        <v>0.9385</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4795</v>
+        <v>0.8736</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4914</v>
+        <v>0.0649</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5343</v>
+        <v>1.7876</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3353</v>
+        <v>-0.538</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1989</v>
+        <v>2.3256</v>
       </c>
       <c r="G20" t="n">
-        <v>4.4067</v>
+        <v>0.8277</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7979</v>
+        <v>-0.6903</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6088</v>
+        <v>1.518</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7694</v>
+        <v>-0.3746</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3542</v>
+        <v>-1.4655</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4152</v>
+        <v>1.0909</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6373</v>
+        <v>1.2023</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4437</v>
+        <v>0.7752</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1936</v>
+        <v>0.4271</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.3501</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.4377</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5429</v>
+        <v>0.5248</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8736</v>
+        <v>0.0541</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3307</v>
+        <v>0.4708</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8512</v>
+        <v>-0.6778</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.6287</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1107</v>
+        <v>-0.0491</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3387</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1199</v>
+        <v>0.0535</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2225</v>
+        <v>0.2842</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0764</v>
+        <v>-0.7604</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1866</v>
+        <v>-0.9631</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1102</v>
+        <v>0.2027</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1125</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0068</v>
+        <v>0.3091</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7395</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9333</v>
+        <v>-0.9789</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3275</v>
+        <v>-2.7687</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3941</v>
+        <v>1.7897</v>
       </c>
       <c r="G23" t="n">
         <v>0.4439</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2021</v>
+        <v>0.7523</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1286</v>
+        <v>0.6874</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3307</v>
+        <v>0.0649</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3847</v>
+        <v>-4.088</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7776</v>
+        <v>-3.6658</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6072</v>
+        <v>-0.4222</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2747</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1747</v>
+        <v>0.122</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1557</v>
+        <v>0.3407</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3252</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.532</v>
+        <v>19.2773</v>
       </c>
       <c r="E25" t="n">
-        <v>8.785599999999997</v>
+        <v>8.785399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>9.746300000000002</v>
+        <v>10.4913</v>
       </c>
       <c r="G25" t="n">
         <v>19.9854</v>
@@ -2404,13 +2404,13 @@
         <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>5.9424</v>
+        <v>6.687399999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>3.460799999999999</v>
+        <v>3.460999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>2.481300000000001</v>
+        <v>3.226500000000001</v>
       </c>
       <c r="V25" t="n">
         <v>1.3044</v>
